--- a/shai-nadlan-demo/e2e/fixtures/real-excel.xlsx
+++ b/shai-nadlan-demo/e2e/fixtures/real-excel.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>רוטשילד 12 דירה 4</t>
+          <t>רוטשילד 12 קומה 1 דירה 4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -531,9 +531,6 @@
       </c>
       <c r="E4" t="n">
         <v>78</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -569,7 +566,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>רוטשילד 12 דירה 7</t>
+          <t>רוטשילד 12 קומה 4 דירה 7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,9 +584,6 @@
       </c>
       <c r="E5" t="n">
         <v>95</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -673,64 +667,112 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>הרצל 45</t>
+          <t>רוטשילד 12 קומה 2 דירה 5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>חיפה</t>
+          <t>תל אביב</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>מסחרי</t>
-        </is>
+          <t>דירה</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>240</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>לפי הסכם</t>
-        </is>
+        <v>80</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>אורי מזרחי</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>050-4443322</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>6500</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>46054</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>46418</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1800000</v>
+        <v>2500000</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>2100000</v>
+        <v>3150000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>הרצל 45</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>חיפה</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>מסחרי</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>240</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>לפי הסכם</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>ויצמן 8</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>דירה</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" t="n">
         <v>82</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>5500</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L9" s="3" t="n">
         <v>2100000</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>2400000</v>
       </c>
     </row>
